--- a/exports/trend_1d/GODREJPROP_full_report.xlsx
+++ b/exports/trend_1d/GODREJPROP_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:U83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>8.970000000000001</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42072</v>
+        <v>42073</v>
       </c>
       <c r="H2" t="n">
-        <v>278.45</v>
+        <v>272.35</v>
       </c>
       <c r="I2" t="n">
         <v>277.8100021191256</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K2" t="n">
-        <v>6.34</v>
+        <v>4.01</v>
       </c>
       <c r="L2" t="n">
         <v>2.43</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>10.6</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42095</v>
+        <v>42100</v>
       </c>
       <c r="H3" t="n">
-        <v>258.64</v>
+        <v>271.6</v>
       </c>
       <c r="I3" t="n">
         <v>269.1875463101454</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K3" t="n">
-        <v>5.03</v>
+        <v>0.28</v>
       </c>
       <c r="L3" t="n">
         <v>2.46</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>14.82</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42118</v>
+        <v>42121</v>
       </c>
       <c r="H4" t="n">
-        <v>244.95</v>
+        <v>241</v>
       </c>
       <c r="I4" t="n">
         <v>243.3286893780383</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K4" t="n">
-        <v>-9.81</v>
+        <v>-11.27</v>
       </c>
       <c r="L4" t="n">
-        <v>10.53</v>
+        <v>12.33</v>
       </c>
       <c r="M4" t="n">
         <v>0.5</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>12.25</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42152</v>
+        <v>42153</v>
       </c>
       <c r="H5" t="n">
-        <v>263.64</v>
+        <v>268.05</v>
       </c>
       <c r="I5" t="n">
         <v>263.8567877501386</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K5" t="n">
-        <v>-9.390000000000001</v>
+        <v>-11.22</v>
       </c>
       <c r="L5" t="n">
         <v>13.67</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>11.4</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H6" t="n">
-        <v>309.55</v>
+        <v>289.5</v>
       </c>
       <c r="I6" t="n">
         <v>289.9744633920829</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K6" t="n">
-        <v>15.48</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
         <v>11.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.92</v>
+        <v>3.28</v>
       </c>
       <c r="N6" t="n">
-        <v>5.26</v>
+        <v>6.48</v>
       </c>
       <c r="O6" t="n">
         <v>1.67</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>22.01</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42283</v>
+        <v>42284</v>
       </c>
       <c r="H7" t="n">
-        <v>324.05</v>
+        <v>338.85</v>
       </c>
       <c r="I7" t="n">
         <v>331.9805914245805</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K7" t="n">
-        <v>-11.93</v>
+        <v>-17.05</v>
       </c>
       <c r="L7" t="n">
-        <v>16.23</v>
+        <v>18.6</v>
       </c>
       <c r="M7" t="n">
         <v>1.97</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>15.57</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42312</v>
+        <v>42313</v>
       </c>
       <c r="H8" t="n">
-        <v>337.35</v>
+        <v>323.5</v>
       </c>
       <c r="I8" t="n">
         <v>326.2593179527661</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.44</v>
+        <v>-4.53</v>
       </c>
       <c r="L8" t="n">
-        <v>4.83</v>
+        <v>5.86</v>
       </c>
       <c r="M8" t="n">
         <v>0.59</v>
       </c>
       <c r="N8" t="n">
-        <v>3.06</v>
+        <v>4.11</v>
       </c>
       <c r="O8" t="n">
         <v>4.57</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>16.13</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42451</v>
+        <v>42452</v>
       </c>
       <c r="H9" t="n">
-        <v>291.35</v>
+        <v>297.75</v>
       </c>
       <c r="I9" t="n">
         <v>296.9496109787892</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K9" t="n">
-        <v>9.94</v>
+        <v>7.96</v>
       </c>
       <c r="L9" t="n">
         <v>9.119999999999999</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.19</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42622</v>
+        <v>42625</v>
       </c>
       <c r="H10" t="n">
-        <v>349.2</v>
+        <v>339.75</v>
       </c>
       <c r="I10" t="n">
         <v>344.1221960591503</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K10" t="n">
-        <v>17.28</v>
+        <v>14.11</v>
       </c>
       <c r="L10" t="n">
         <v>3.9</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>8.42</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42663</v>
+        <v>42664</v>
       </c>
       <c r="H11" t="n">
-        <v>358.65</v>
+        <v>362.45</v>
       </c>
       <c r="I11" t="n">
         <v>359.5843010157137</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.56</v>
+        <v>-6.68</v>
       </c>
       <c r="L11" t="n">
-        <v>7.08</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M11" t="n">
         <v>1.47</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.75</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42683</v>
+        <v>42684</v>
       </c>
       <c r="H12" t="n">
-        <v>350.45</v>
+        <v>340.1</v>
       </c>
       <c r="I12" t="n">
         <v>340.1105020013187</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.31</v>
+        <v>-6.17</v>
       </c>
       <c r="L12" t="n">
         <v>18.58</v>
@@ -1125,7 +1268,7 @@
         <v>17.83</v>
       </c>
       <c r="N12" t="n">
-        <v>2.42</v>
+        <v>2.95</v>
       </c>
       <c r="O12" t="n">
         <v>1.06</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>15</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42737</v>
+        <v>42738</v>
       </c>
       <c r="H13" t="n">
-        <v>313.7</v>
+        <v>321.2</v>
       </c>
       <c r="I13" t="n">
         <v>319.0071155900134</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K13" t="n">
-        <v>7.76</v>
+        <v>5.56</v>
       </c>
       <c r="L13" t="n">
         <v>4.03</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.9</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42949</v>
+        <v>42950</v>
       </c>
       <c r="H14" t="n">
-        <v>505.1</v>
+        <v>499.9</v>
       </c>
       <c r="I14" t="n">
         <v>503.0570781416567</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K14" t="n">
-        <v>57.25</v>
+        <v>55.64</v>
       </c>
       <c r="L14" t="n">
         <v>3.5</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>8</v>
+      </c>
+      <c r="U14" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>9.4</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42971</v>
+        <v>42975</v>
       </c>
       <c r="H15" t="n">
-        <v>519.6</v>
+        <v>540.55</v>
       </c>
       <c r="I15" t="n">
         <v>535.192445237974</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.94</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>4.85</v>
+        <v>10.62</v>
       </c>
       <c r="M15" t="n">
         <v>0.66</v>
       </c>
       <c r="N15" t="n">
-        <v>2.27</v>
+        <v>4.03</v>
       </c>
       <c r="O15" t="n">
         <v>-1.03</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>8.24</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43165</v>
+        <v>43166</v>
       </c>
       <c r="H16" t="n">
-        <v>762.4</v>
+        <v>745.35</v>
       </c>
       <c r="I16" t="n">
         <v>759.4783557881809</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K16" t="n">
-        <v>41.04</v>
+        <v>37.89</v>
       </c>
       <c r="L16" t="n">
         <v>3.43</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>11.57</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43207</v>
+        <v>43208</v>
       </c>
       <c r="H17" t="n">
-        <v>764.2</v>
+        <v>789.05</v>
       </c>
       <c r="I17" t="n">
         <v>775.3061631486911</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.53</v>
+        <v>-5.86</v>
       </c>
       <c r="L17" t="n">
-        <v>5.32</v>
+        <v>6.53</v>
       </c>
       <c r="M17" t="n">
         <v>1.73</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.82</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43237</v>
+        <v>43238</v>
       </c>
       <c r="H18" t="n">
-        <v>798.05</v>
+        <v>776.9</v>
       </c>
       <c r="I18" t="n">
         <v>785.6751106230388</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K18" t="n">
-        <v>1.14</v>
+        <v>-1.54</v>
       </c>
       <c r="L18" t="n">
         <v>3.04</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>14.94</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43257</v>
+        <v>43258</v>
       </c>
       <c r="H19" t="n">
-        <v>726.2</v>
+        <v>787.6</v>
       </c>
       <c r="I19" t="n">
         <v>780.3230483473174</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>6.53</v>
+        <v>-1.38</v>
       </c>
       <c r="L19" t="n">
         <v>3.49</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>1.62</v>
       </c>
       <c r="N19" t="n">
-        <v>2.81</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O19" t="n">
         <v>-2.65</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>14.63</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43294</v>
+        <v>43297</v>
       </c>
       <c r="H20" t="n">
-        <v>705.55</v>
+        <v>670.8</v>
       </c>
       <c r="I20" t="n">
         <v>697.2174979793251</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K20" t="n">
-        <v>-10.42</v>
+        <v>-14.83</v>
       </c>
       <c r="L20" t="n">
-        <v>12.06</v>
+        <v>15.91</v>
       </c>
       <c r="M20" t="n">
         <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>3.14</v>
+        <v>4.93</v>
       </c>
       <c r="O20" t="n">
         <v>8.449999999999999</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>11.76</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43312</v>
+        <v>43313</v>
       </c>
       <c r="H21" t="n">
-        <v>714.75</v>
+        <v>743.25</v>
       </c>
       <c r="I21" t="n">
         <v>727.3746346727646</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K21" t="n">
-        <v>-6.55</v>
+        <v>-10.8</v>
       </c>
       <c r="L21" t="n">
-        <v>6.66</v>
+        <v>12</v>
       </c>
       <c r="M21" t="n">
         <v>0.91</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>11.62</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43355</v>
+        <v>43357</v>
       </c>
       <c r="H22" t="n">
-        <v>658.15</v>
+        <v>654.55</v>
       </c>
       <c r="I22" t="n">
         <v>656.9047386273842</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K22" t="n">
-        <v>-11.45</v>
+        <v>-11.93</v>
       </c>
       <c r="L22" t="n">
         <v>12.53</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>10.08</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43399</v>
+        <v>43402</v>
       </c>
       <c r="H23" t="n">
-        <v>528.75</v>
+        <v>585.85</v>
       </c>
       <c r="I23" t="n">
         <v>583.578758778465</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K23" t="n">
-        <v>19.22</v>
+        <v>10.5</v>
       </c>
       <c r="L23" t="n">
         <v>2.36</v>
@@ -1752,7 +2027,7 @@
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>7.28</v>
+        <v>10.8</v>
       </c>
       <c r="O23" t="n">
         <v>-0.55</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>22.38</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43585</v>
+        <v>43587</v>
       </c>
       <c r="H24" t="n">
-        <v>829.9</v>
+        <v>820.4</v>
       </c>
       <c r="I24" t="n">
         <v>827.445869145798</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K24" t="n">
-        <v>41.66</v>
+        <v>40.04</v>
       </c>
       <c r="L24" t="n">
         <v>10.58</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>7</v>
+      </c>
+      <c r="U24" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>15.72</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43609</v>
+        <v>43612</v>
       </c>
       <c r="H25" t="n">
-        <v>880.35</v>
+        <v>919.55</v>
       </c>
       <c r="I25" t="n">
         <v>880.8814893994128</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K25" t="n">
-        <v>-7.31</v>
+        <v>-12.09</v>
       </c>
       <c r="L25" t="n">
-        <v>9.42</v>
+        <v>12.85</v>
       </c>
       <c r="M25" t="n">
         <v>2.84</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>14.27</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H26" t="n">
-        <v>925.05</v>
+        <v>889.45</v>
       </c>
       <c r="I26" t="n">
         <v>915.0624569096865</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K26" t="n">
-        <v>0.6</v>
+        <v>-3.27</v>
       </c>
       <c r="L26" t="n">
         <v>8.65</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>18.53</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43717</v>
+        <v>43719</v>
       </c>
       <c r="H27" t="n">
-        <v>895</v>
+        <v>954.9</v>
       </c>
       <c r="I27" t="n">
         <v>949.8721339553224</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.62</v>
+        <v>-7.36</v>
       </c>
       <c r="L27" t="n">
         <v>12.09</v>
@@ -1980,7 +2303,7 @@
         <v>2.18</v>
       </c>
       <c r="N27" t="n">
-        <v>2.88</v>
+        <v>6.69</v>
       </c>
       <c r="O27" t="n">
         <v>-3.85</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>11.4</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43782</v>
+        <v>43783</v>
       </c>
       <c r="H28" t="n">
-        <v>933.8</v>
+        <v>919.7</v>
       </c>
       <c r="I28" t="n">
         <v>931.8699149614031</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.21</v>
+        <v>-3.69</v>
       </c>
       <c r="L28" t="n">
         <v>7.48</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>11.67</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43825</v>
+        <v>43826</v>
       </c>
       <c r="H29" t="n">
-        <v>949.7</v>
+        <v>957.6</v>
       </c>
       <c r="I29" t="n">
         <v>953.7154221273048</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.26</v>
+        <v>-4.12</v>
       </c>
       <c r="L29" t="n">
-        <v>3.7</v>
+        <v>4.48</v>
       </c>
       <c r="M29" t="n">
         <v>0.62</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H30" t="n">
-        <v>1080.3</v>
+        <v>989.9</v>
       </c>
       <c r="I30" t="n">
         <v>993.8219247266773</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K30" t="n">
-        <v>12.81</v>
+        <v>3.37</v>
       </c>
       <c r="L30" t="n">
         <v>4.13</v>
@@ -2151,7 +2510,7 @@
         <v>1.62</v>
       </c>
       <c r="N30" t="n">
-        <v>4.1</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="O30" t="n">
         <v>0.83</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>17.13</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43866</v>
+        <v>43867</v>
       </c>
       <c r="H31" t="n">
-        <v>1151.4</v>
+        <v>1168.65</v>
       </c>
       <c r="I31" t="n">
         <v>1159.422641874252</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>-16.31</v>
+        <v>-18.06</v>
       </c>
       <c r="L31" t="n">
         <v>20.14</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,25 +2627,25 @@
         <v>14.87</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43888</v>
+        <v>43889</v>
       </c>
       <c r="H32" t="n">
-        <v>1039.75</v>
+        <v>1003.05</v>
       </c>
       <c r="I32" t="n">
         <v>1016.321993154235</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K32" t="n">
-        <v>-11.03</v>
+        <v>-14.17</v>
       </c>
       <c r="L32" t="n">
-        <v>11.52</v>
+        <v>15.71</v>
       </c>
       <c r="M32" t="n">
-        <v>0.99</v>
+        <v>2.02</v>
       </c>
       <c r="N32" t="n">
         <v>3.91</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>13.78</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43980</v>
+        <v>43983</v>
       </c>
       <c r="H33" t="n">
-        <v>688.4</v>
+        <v>715.65</v>
       </c>
       <c r="I33" t="n">
         <v>690.9875927225065</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K33" t="n">
-        <v>31.37</v>
+        <v>28.65</v>
       </c>
       <c r="L33" t="n">
         <v>4.08</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>14.7</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44139</v>
+        <v>44140</v>
       </c>
       <c r="H34" t="n">
-        <v>978.35</v>
+        <v>912.15</v>
       </c>
       <c r="I34" t="n">
         <v>944.0432966522847</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K34" t="n">
-        <v>36.71</v>
+        <v>27.46</v>
       </c>
       <c r="L34" t="n">
         <v>3.3</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>24.31</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44158</v>
+        <v>44159</v>
       </c>
       <c r="H35" t="n">
-        <v>1088.25</v>
+        <v>1118.5</v>
       </c>
       <c r="I35" t="n">
         <v>1118.433813066436</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>-19.31</v>
+        <v>-22.62</v>
       </c>
       <c r="L35" t="n">
-        <v>23.01</v>
+        <v>24.87</v>
       </c>
       <c r="M35" t="n">
         <v>1.33</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>14.34</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44221</v>
+        <v>44223</v>
       </c>
       <c r="H36" t="n">
-        <v>1327.2</v>
+        <v>1297.15</v>
       </c>
       <c r="I36" t="n">
         <v>1318.710084865466</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K36" t="n">
-        <v>18.66</v>
+        <v>15.97</v>
       </c>
       <c r="L36" t="n">
         <v>3.91</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>13.51</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44236</v>
+        <v>44237</v>
       </c>
       <c r="H37" t="n">
-        <v>1424.6</v>
+        <v>1464.75</v>
       </c>
       <c r="I37" t="n">
         <v>1433.21851874252</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K37" t="n">
-        <v>-9.83</v>
+        <v>-12.92</v>
       </c>
       <c r="L37" t="n">
-        <v>12.71</v>
+        <v>13.33</v>
       </c>
       <c r="M37" t="n">
         <v>1.3</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>14.36</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44272</v>
+        <v>44273</v>
       </c>
       <c r="H38" t="n">
-        <v>1389.9</v>
+        <v>1346.05</v>
       </c>
       <c r="I38" t="n">
         <v>1363.705226536236</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K38" t="n">
-        <v>-5.11</v>
+        <v>-8.1</v>
       </c>
       <c r="L38" t="n">
-        <v>6.81</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="M38" t="n">
         <v>4.5</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>16.07</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44348</v>
+        <v>44349</v>
       </c>
       <c r="H39" t="n">
-        <v>1361.1</v>
+        <v>1390.65</v>
       </c>
       <c r="I39" t="n">
         <v>1378.998327683557</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.12</v>
+        <v>-3.31</v>
       </c>
       <c r="L39" t="n">
         <v>7.65</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>9.789999999999999</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44426</v>
+        <v>44428</v>
       </c>
       <c r="H40" t="n">
-        <v>1507.1</v>
+        <v>1484.95</v>
       </c>
       <c r="I40" t="n">
         <v>1488.908689841201</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K40" t="n">
-        <v>8.369999999999999</v>
+        <v>6.78</v>
       </c>
       <c r="L40" t="n">
         <v>4.26</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,25 +3248,25 @@
         <v>10.06</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44440</v>
+        <v>44441</v>
       </c>
       <c r="H41" t="n">
-        <v>1560.55</v>
+        <v>1595.4</v>
       </c>
       <c r="I41" t="n">
         <v>1588.00492759904</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K41" t="n">
-        <v>-5.09</v>
+        <v>-7.44</v>
       </c>
       <c r="L41" t="n">
-        <v>5.92</v>
+        <v>8.4</v>
       </c>
       <c r="M41" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="N41" t="n">
         <v>4.81</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>10.06</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44518</v>
+        <v>44522</v>
       </c>
       <c r="H42" t="n">
-        <v>2177.4</v>
+        <v>2116.2</v>
       </c>
       <c r="I42" t="n">
         <v>2170.959241070921</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="K42" t="n">
-        <v>36.48</v>
+        <v>32.64</v>
       </c>
       <c r="L42" t="n">
         <v>2.22</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>15.99</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44645</v>
+        <v>44648</v>
       </c>
       <c r="H43" t="n">
-        <v>1622.95</v>
+        <v>1628.95</v>
       </c>
       <c r="I43" t="n">
         <v>1625.474037701547</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K43" t="n">
-        <v>23.31</v>
+        <v>23.02</v>
       </c>
       <c r="L43" t="n">
         <v>7.27</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>5</v>
+      </c>
+      <c r="U43" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>11.53</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44673</v>
+        <v>44676</v>
       </c>
       <c r="H44" t="n">
-        <v>1574.4</v>
+        <v>1510.8</v>
       </c>
       <c r="I44" t="n">
         <v>1551.726948549089</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.35</v>
+        <v>-7.25</v>
       </c>
       <c r="L44" t="n">
-        <v>5.53</v>
+        <v>7.7</v>
       </c>
       <c r="M44" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="N44" t="n">
         <v>4.6</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>11.2</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44756</v>
+        <v>44757</v>
       </c>
       <c r="H45" t="n">
-        <v>1317.45</v>
+        <v>1343.55</v>
       </c>
       <c r="I45" t="n">
         <v>1336.933079925741</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K45" t="n">
-        <v>12.8</v>
+        <v>11.07</v>
       </c>
       <c r="L45" t="n">
         <v>10.44</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44777</v>
+        <v>44778</v>
       </c>
       <c r="H46" t="n">
-        <v>1391.4</v>
+        <v>1373.85</v>
       </c>
       <c r="I46" t="n">
         <v>1391.132768297316</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K46" t="n">
-        <v>3.56</v>
+        <v>2.26</v>
       </c>
       <c r="L46" t="n">
         <v>2.2</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>11.82</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44813</v>
+        <v>44816</v>
       </c>
       <c r="H47" t="n">
-        <v>1409.5</v>
+        <v>1459.6</v>
       </c>
       <c r="I47" t="n">
         <v>1443.059419944006</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.59</v>
+        <v>-6.24</v>
       </c>
       <c r="L47" t="n">
-        <v>5.62</v>
+        <v>7.98</v>
       </c>
       <c r="M47" t="n">
         <v>1.08</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>10.72</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44820</v>
+        <v>44823</v>
       </c>
       <c r="H48" t="n">
-        <v>1331</v>
+        <v>1308.6</v>
       </c>
       <c r="I48" t="n">
         <v>1313.024139970145</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K48" t="n">
-        <v>-8.81</v>
+        <v>-10.35</v>
       </c>
       <c r="L48" t="n">
-        <v>9.83</v>
+        <v>10.52</v>
       </c>
       <c r="M48" t="n">
         <v>2</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>12.52</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44876</v>
+        <v>44879</v>
       </c>
       <c r="H49" t="n">
-        <v>1292.8</v>
+        <v>1309.65</v>
       </c>
       <c r="I49" t="n">
         <v>1293.470841157625</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K49" t="n">
-        <v>1.21</v>
+        <v>-0.08</v>
       </c>
       <c r="L49" t="n">
         <v>2.64</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>11.91</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44915</v>
+        <v>44916</v>
       </c>
       <c r="H50" t="n">
-        <v>1275.8</v>
+        <v>1254.4</v>
       </c>
       <c r="I50" t="n">
         <v>1256.119989232666</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.58</v>
+        <v>-4.22</v>
       </c>
       <c r="L50" t="n">
-        <v>4.38</v>
+        <v>4.55</v>
       </c>
       <c r="M50" t="n">
         <v>0.29</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>10.63</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44991</v>
+        <v>44993</v>
       </c>
       <c r="H51" t="n">
-        <v>1165.9</v>
+        <v>1182.3</v>
       </c>
       <c r="I51" t="n">
         <v>1173.17889288504</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K51" t="n">
-        <v>7.06</v>
+        <v>5.75</v>
       </c>
       <c r="L51" t="n">
         <v>3.63</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8.51</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45006</v>
+        <v>45007</v>
       </c>
       <c r="H52" t="n">
-        <v>1097.45</v>
+        <v>1084.45</v>
       </c>
       <c r="I52" t="n">
         <v>1087.457215580153</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K52" t="n">
-        <v>-7.18</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="L52" t="n">
         <v>9.380000000000001</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45021</v>
+        <v>45022</v>
       </c>
       <c r="H53" t="n">
-        <v>1056.5</v>
+        <v>1125.35</v>
       </c>
       <c r="I53" t="n">
         <v>1104.626545155024</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K53" t="n">
-        <v>2.58</v>
+        <v>-3.77</v>
       </c>
       <c r="L53" t="n">
-        <v>1.89</v>
+        <v>4.12</v>
       </c>
       <c r="M53" t="n">
         <v>1.31</v>
       </c>
       <c r="N53" t="n">
-        <v>1.4</v>
+        <v>6.52</v>
       </c>
       <c r="O53" t="n">
         <v>-1.18</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>11.94</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45140</v>
+        <v>45141</v>
       </c>
       <c r="H54" t="n">
-        <v>1659.8</v>
+        <v>1573</v>
       </c>
       <c r="I54" t="n">
         <v>1625.128500604258</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K54" t="n">
-        <v>47.49</v>
+        <v>39.78</v>
       </c>
       <c r="L54" t="n">
         <v>6.38</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>5</v>
+      </c>
+      <c r="U54" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>12.53</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45173</v>
+        <v>45174</v>
       </c>
       <c r="H55" t="n">
-        <v>1650.5</v>
+        <v>1659.7</v>
       </c>
       <c r="I55" t="n">
         <v>1659.450871470175</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K55" t="n">
-        <v>-4.93</v>
+        <v>-5.51</v>
       </c>
       <c r="L55" t="n">
         <v>6.47</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,25 +4283,25 @@
         <v>5.93</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45189</v>
+        <v>45190</v>
       </c>
       <c r="H56" t="n">
-        <v>1588.4</v>
+        <v>1553.6</v>
       </c>
       <c r="I56" t="n">
         <v>1582.565094675179</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K56" t="n">
-        <v>-4.3</v>
+        <v>-6.39</v>
       </c>
       <c r="L56" t="n">
-        <v>4.52</v>
+        <v>6.76</v>
       </c>
       <c r="M56" t="n">
-        <v>0.23</v>
+        <v>0.52</v>
       </c>
       <c r="N56" t="n">
         <v>3.66</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>9.99</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45208</v>
+        <v>45209</v>
       </c>
       <c r="H57" t="n">
-        <v>1630.65</v>
+        <v>1722.75</v>
       </c>
       <c r="I57" t="n">
         <v>1678.211149121712</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.96</v>
+        <v>-10.89</v>
       </c>
       <c r="L57" t="n">
-        <v>8.58</v>
+        <v>12.41</v>
       </c>
       <c r="M57" t="n">
         <v>0.97</v>
       </c>
       <c r="N57" t="n">
-        <v>4.73</v>
+        <v>5.65</v>
       </c>
       <c r="O57" t="n">
         <v>-2.19</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>11.14</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45222</v>
+        <v>45224</v>
       </c>
       <c r="H58" t="n">
-        <v>1630.2</v>
+        <v>1582</v>
       </c>
       <c r="I58" t="n">
         <v>1584.08826780512</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K58" t="n">
-        <v>-5.37</v>
+        <v>-8.17</v>
       </c>
       <c r="L58" t="n">
-        <v>6.32</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="M58" t="n">
         <v>1.3</v>
       </c>
       <c r="N58" t="n">
-        <v>1.85</v>
+        <v>2.96</v>
       </c>
       <c r="O58" t="n">
         <v>5.65</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>11.23</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45231</v>
+        <v>45232</v>
       </c>
       <c r="H59" t="n">
-        <v>1664.25</v>
+        <v>1716</v>
       </c>
       <c r="I59" t="n">
         <v>1710.776533988742</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K59" t="n">
-        <v>-5.2</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>7.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="M59" t="n">
-        <v>0.14</v>
+        <v>0.76</v>
       </c>
       <c r="N59" t="n">
-        <v>2.32</v>
+        <v>3.11</v>
       </c>
       <c r="O59" t="n">
         <v>-2.96</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>9</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H60" t="n">
-        <v>2319.2</v>
+        <v>2205.25</v>
       </c>
       <c r="I60" t="n">
         <v>2286.539971912196</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K60" t="n">
-        <v>35.15</v>
+        <v>28.51</v>
       </c>
       <c r="L60" t="n">
         <v>2.39</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>5</v>
+      </c>
+      <c r="U60" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>14.38</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45379</v>
+        <v>45383</v>
       </c>
       <c r="H61" t="n">
-        <v>2300.1</v>
+        <v>2389.7</v>
       </c>
       <c r="I61" t="n">
         <v>2377.60229927913</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K61" t="n">
-        <v>-4.3</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>6.22</v>
+        <v>9.51</v>
       </c>
       <c r="M61" t="n">
         <v>1.41</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>11.52</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H62" t="n">
-        <v>2964.75</v>
+        <v>2583.95</v>
       </c>
       <c r="I62" t="n">
         <v>2595.34729375338</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K62" t="n">
-        <v>24.06</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="L62" t="n">
         <v>4.26</v>
@@ -3975,7 +4718,7 @@
         <v>2.54</v>
       </c>
       <c r="N62" t="n">
-        <v>4.34</v>
+        <v>12.84</v>
       </c>
       <c r="O62" t="n">
         <v>3.9</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>22.46</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45455</v>
+        <v>45456</v>
       </c>
       <c r="H63" t="n">
-        <v>2928.2</v>
+        <v>3030.75</v>
       </c>
       <c r="I63" t="n">
         <v>3025.032442059762</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K63" t="n">
-        <v>-13.32</v>
+        <v>-17.29</v>
       </c>
       <c r="L63" t="n">
-        <v>14.16</v>
+        <v>17.96</v>
       </c>
       <c r="M63" t="n">
         <v>1.2</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>14.18</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="H64" t="n">
-        <v>3127.2</v>
+        <v>3001.55</v>
       </c>
       <c r="I64" t="n">
         <v>3061.289032706567</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K64" t="n">
-        <v>3.18</v>
+        <v>-0.96</v>
       </c>
       <c r="L64" t="n">
         <v>3.16</v>
@@ -4089,7 +4856,7 @@
         <v>1.19</v>
       </c>
       <c r="N64" t="n">
-        <v>3.48</v>
+        <v>4.02</v>
       </c>
       <c r="O64" t="n">
         <v>3.5</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>14.06</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45555</v>
+        <v>45558</v>
       </c>
       <c r="H65" t="n">
-        <v>2988</v>
+        <v>3192.35</v>
       </c>
       <c r="I65" t="n">
         <v>3055.09695641393</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K65" t="n">
-        <v>0.45</v>
+        <v>-6.36</v>
       </c>
       <c r="L65" t="n">
-        <v>4.38</v>
+        <v>6.76</v>
       </c>
       <c r="M65" t="n">
         <v>4.39</v>
       </c>
       <c r="N65" t="n">
-        <v>3.22</v>
+        <v>6.84</v>
       </c>
       <c r="O65" t="n">
         <v>-4.02</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>11.68</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45568</v>
+        <v>45569</v>
       </c>
       <c r="H66" t="n">
-        <v>3071.15</v>
+        <v>2897.45</v>
       </c>
       <c r="I66" t="n">
         <v>2990.614061319669</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.8</v>
+        <v>-9.24</v>
       </c>
       <c r="L66" t="n">
-        <v>5.99</v>
+        <v>9.5</v>
       </c>
       <c r="M66" t="n">
         <v>2.23</v>
       </c>
       <c r="N66" t="n">
-        <v>5.57</v>
+        <v>5.66</v>
       </c>
       <c r="O66" t="n">
         <v>6.84</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,25 +5042,25 @@
         <v>15.59</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45618</v>
+        <v>45621</v>
       </c>
       <c r="H67" t="n">
-        <v>2857.15</v>
+        <v>2943.05</v>
       </c>
       <c r="I67" t="n">
         <v>2891.708353124685</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K67" t="n">
-        <v>1.39</v>
+        <v>-1.57</v>
       </c>
       <c r="L67" t="n">
         <v>11.81</v>
       </c>
       <c r="M67" t="n">
-        <v>1.11</v>
+        <v>1.97</v>
       </c>
       <c r="N67" t="n">
         <v>5.63</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>10.62</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45660</v>
+        <v>45663</v>
       </c>
       <c r="H68" t="n">
-        <v>2734.1</v>
+        <v>2616.1</v>
       </c>
       <c r="I68" t="n">
         <v>2730.455621614739</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K68" t="n">
-        <v>-7.1</v>
+        <v>-11.11</v>
       </c>
       <c r="L68" t="n">
-        <v>7.44</v>
+        <v>11.53</v>
       </c>
       <c r="M68" t="n">
         <v>3.63</v>
       </c>
       <c r="N68" t="n">
-        <v>4.29</v>
+        <v>4.32</v>
       </c>
       <c r="O68" t="n">
         <v>3.01</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>13.06</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45777</v>
+        <v>45779</v>
       </c>
       <c r="H69" t="n">
-        <v>2161.5</v>
+        <v>2249.3</v>
       </c>
       <c r="I69" t="n">
         <v>2213.155634092914</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K69" t="n">
-        <v>17.38</v>
+        <v>14.02</v>
       </c>
       <c r="L69" t="n">
         <v>5.68</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>5</v>
+      </c>
+      <c r="U69" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>13.45</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45848</v>
+        <v>45849</v>
       </c>
       <c r="H70" t="n">
-        <v>2256.2</v>
+        <v>2206.3</v>
       </c>
       <c r="I70" t="n">
         <v>2251.198546908297</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K70" t="n">
-        <v>0.31</v>
+        <v>-1.91</v>
       </c>
       <c r="L70" t="n">
         <v>13.4</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="H71" t="n">
-        <v>2087.6</v>
+        <v>2145.2</v>
       </c>
       <c r="I71" t="n">
         <v>2102.101429770815</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K71" t="n">
-        <v>5.38</v>
+        <v>2.77</v>
       </c>
       <c r="L71" t="n">
         <v>9.140000000000001</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>7.98</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="H72" t="n">
-        <v>2019.1</v>
+        <v>1967.4</v>
       </c>
       <c r="I72" t="n">
         <v>1979.677698090738</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K72" t="n">
-        <v>-5.88</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="L72" t="n">
-        <v>6.21</v>
+        <v>8.85</v>
       </c>
       <c r="M72" t="n">
         <v>0.41</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>9.26</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="H73" t="n">
-        <v>2057.4</v>
+        <v>2135.6</v>
       </c>
       <c r="I73" t="n">
         <v>2123.422982282667</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K73" t="n">
-        <v>-4.57</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="L73" t="n">
-        <v>6.99</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="M73" t="n">
         <v>0.84</v>
       </c>
       <c r="N73" t="n">
-        <v>3.13</v>
+        <v>3.8</v>
       </c>
       <c r="O73" t="n">
         <v>-2.56</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>9.41</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="H74" t="n">
-        <v>2193.7</v>
+        <v>2142.7</v>
       </c>
       <c r="I74" t="n">
         <v>2150.16121349309</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K74" t="n">
-        <v>2.72</v>
+        <v>0.33</v>
       </c>
       <c r="L74" t="n">
         <v>3.19</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>9.65</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="H75" t="n">
-        <v>2068.5</v>
+        <v>2124.2</v>
       </c>
       <c r="I75" t="n">
         <v>2107.674610770812</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K75" t="n">
-        <v>3.46</v>
+        <v>0.86</v>
       </c>
       <c r="L75" t="n">
         <v>4.23</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4752,28 +5663,28 @@
         <v>7.81</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="H76" t="n">
-        <v>2095.1</v>
+        <v>1991.5</v>
       </c>
       <c r="I76" t="n">
         <v>1993.038680585943</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K76" t="n">
-        <v>-1.37</v>
+        <v>-6.25</v>
       </c>
       <c r="L76" t="n">
-        <v>3.13</v>
+        <v>6.67</v>
       </c>
       <c r="M76" t="n">
         <v>0.54</v>
       </c>
       <c r="N76" t="n">
-        <v>2.02</v>
+        <v>4.94</v>
       </c>
       <c r="O76" t="n">
         <v>2.69</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>10.51</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="H77" t="n">
-        <v>1699.8</v>
+        <v>1801.4</v>
       </c>
       <c r="I77" t="n">
         <v>1737.169118992039</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K77" t="n">
-        <v>14.65</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="L77" t="n">
         <v>4.95</v>
@@ -4839,7 +5762,19 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,22 +5801,22 @@
         <v>15.88</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H78" t="n">
-        <v>1667.3</v>
+        <v>1645.6</v>
       </c>
       <c r="I78" t="n">
         <v>1664.307495180934</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K78" t="n">
-        <v>-7.44</v>
+        <v>-8.65</v>
       </c>
       <c r="L78" t="n">
-        <v>8.57</v>
+        <v>11.71</v>
       </c>
       <c r="M78" t="n">
         <v>3.77</v>
@@ -4896,7 +5831,19 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,28 +5870,28 @@
         <v>11.24</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H79" t="n">
-        <v>1605</v>
+        <v>1702.2</v>
       </c>
       <c r="I79" t="n">
         <v>1673.199555693191</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K79" t="n">
-        <v>2.47</v>
+        <v>-3.44</v>
       </c>
       <c r="L79" t="n">
-        <v>3.18</v>
+        <v>4.7</v>
       </c>
       <c r="M79" t="n">
-        <v>3.09</v>
+        <v>5.79</v>
       </c>
       <c r="N79" t="n">
-        <v>5.07</v>
+        <v>6.06</v>
       </c>
       <c r="O79" t="n">
         <v>-1.3</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,25 +5939,25 @@
         <v>13.23</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="H80" t="n">
-        <v>1714.1</v>
+        <v>1686.3</v>
       </c>
       <c r="I80" t="n">
         <v>1708.647991271107</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K80" t="n">
-        <v>0.7</v>
+        <v>-0.93</v>
       </c>
       <c r="L80" t="n">
         <v>3.6</v>
       </c>
       <c r="M80" t="n">
-        <v>1.2</v>
+        <v>1.86</v>
       </c>
       <c r="N80" t="n">
         <v>4.75</v>
@@ -5010,7 +5969,19 @@
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5037,19 +6008,19 @@
         <v>10.56</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="H81" t="n">
-        <v>1766.2</v>
+        <v>1794.5</v>
       </c>
       <c r="I81" t="n">
         <v>1786.740590882345</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K81" t="n">
-        <v>-4.74</v>
+        <v>-6.42</v>
       </c>
       <c r="L81" t="n">
         <v>8.81</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5094,19 +6077,19 @@
         <v>10.58</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="H82" t="n">
-        <v>1982</v>
+        <v>1922.2</v>
       </c>
       <c r="I82" t="n">
         <v>1957.988449216697</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K82" t="n">
-        <v>10.45</v>
+        <v>7.12</v>
       </c>
       <c r="L82" t="n">
         <v>3.08</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>4</v>
+      </c>
+      <c r="U82" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -5175,6 +6170,14 @@
       <c r="Q83" t="n">
         <v>35</v>
       </c>
+      <c r="R83" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10133,7 +11136,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50.7</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="6">
@@ -10143,7 +11146,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -10153,7 +11156,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8">
@@ -10163,7 +11166,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -10173,7 +11176,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -10183,7 +11186,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11">
@@ -10193,7 +11196,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12">
@@ -10203,7 +11206,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -10213,7 +11216,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>42</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="14">
@@ -10223,7 +11226,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.14</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="15">
@@ -10233,7 +11236,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.57</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="16">
@@ -10243,7 +11246,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.62</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="17">
@@ -10253,7 +11256,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>57.25</v>
+        <v>55.64</v>
       </c>
     </row>
     <row r="18">
@@ -10263,7 +11266,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.4</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="19">
@@ -10273,7 +11276,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.03</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="20">
@@ -10283,7 +11286,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.99</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="21">
@@ -10293,7 +11296,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>23.01</v>
+        <v>24.87</v>
       </c>
     </row>
     <row r="22">
@@ -10303,7 +11306,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23">
@@ -10313,7 +11316,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24">
@@ -10323,7 +11326,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.99</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="25">
@@ -10343,7 +11346,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.64</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="27">
@@ -10363,7 +11366,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29">
